--- a/docs/01_Projektorganisation/Projektstrukturplan.xlsx
+++ b/docs/01_Projektorganisation/Projektstrukturplan.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,19 +29,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F497D"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00262626"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -53,7 +42,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -63,16 +52,21 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001F497D"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,7 +80,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,13 +104,55 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F497D"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F497D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F497D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F497D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="medium">
+        <color rgb="002F5597"/>
+      </right>
+      <top style="medium">
+        <color rgb="002F5597"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002F5597"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="008EA9DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="008EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="008EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008EA9DB"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -121,25 +172,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -216,36 +283,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10953750" cy="6438900"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,40 +574,957 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B6"/>
+  <dimension ref="B2:AD38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7.5" customWidth="1" min="1" max="1"/>
+    <col width="7.5" customWidth="1" min="2" max="2"/>
+    <col width="7.5" customWidth="1" min="3" max="3"/>
+    <col width="7.5" customWidth="1" min="4" max="4"/>
+    <col width="7.5" customWidth="1" min="5" max="5"/>
+    <col width="7.5" customWidth="1" min="6" max="6"/>
+    <col width="7.5" customWidth="1" min="7" max="7"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
+    <col width="7.5" customWidth="1" min="9" max="9"/>
+    <col width="7.5" customWidth="1" min="10" max="10"/>
+    <col width="7.5" customWidth="1" min="11" max="11"/>
+    <col width="7.5" customWidth="1" min="12" max="12"/>
+    <col width="7.5" customWidth="1" min="13" max="13"/>
+    <col width="7.5" customWidth="1" min="14" max="14"/>
+    <col width="7.5" customWidth="1" min="15" max="15"/>
+    <col width="7.5" customWidth="1" min="16" max="16"/>
+    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="7.5" customWidth="1" min="18" max="18"/>
+    <col width="7.5" customWidth="1" min="19" max="19"/>
+    <col width="7.5" customWidth="1" min="20" max="20"/>
+    <col width="7.5" customWidth="1" min="21" max="21"/>
+    <col width="7.5" customWidth="1" min="22" max="22"/>
+    <col width="7.5" customWidth="1" min="23" max="23"/>
+    <col width="7.5" customWidth="1" min="24" max="24"/>
+    <col width="7.5" customWidth="1" min="25" max="25"/>
+    <col width="7.5" customWidth="1" min="26" max="26"/>
+    <col width="7.5" customWidth="1" min="27" max="27"/>
+    <col width="7.5" customWidth="1" min="28" max="28"/>
+    <col width="7.5" customWidth="1" min="29" max="29"/>
+    <col width="7.5" customWidth="1" min="30" max="30"/>
+    <col width="7.5" customWidth="1" min="31" max="31"/>
+    <col width="7.5" customWidth="1" min="32" max="32"/>
+    <col width="7.5" customWidth="1" min="33" max="33"/>
+    <col width="7.5" customWidth="1" min="34" max="34"/>
+  </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Projektstrukturplan nach DIN 69901</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Projektstrukturplan (PSP) nach DIN 69901</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Projekt: IT-Ausstattung VektorPlan GmbH | NextLevel IT Solutions GmbH | 5 Teilprojekte, 30 Arbeitspakete</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Hinweis: Untenstehend ist der grafische Projektstrukturplan (PSP) als hochaufloesendes Diagramm eingebettet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Detaillierte Arbeitspaketbeschreibungen finden Sie im Tabellenblatt 'Arbeitspakete-Tabelle'.</t>
-        </is>
-      </c>
+          <t>Projekt: IT-Ausstattung Planungs- und Konstruktionsbüro | Kunde: VektorPlan GmbH | Projektleiter: Jan Kluth</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>1.0 IT-Ausstattung VektorPlan GmbH
+(Schlüsselfertige Büro-Ausstattung)
+Projektleiter: Jan Kluth</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1">
+      <c r="P8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="P9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="5" t="n"/>
+      <c r="AA10" s="5" t="n"/>
+      <c r="AB10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="10" customHeight="1">
+      <c r="D11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Hardware-Ausstattung
+Verantwortlich:
+Marian Bolecke</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Software &amp; Lizenzen
+Verantwortlich:
+Mathias Vonau</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Netzwerk &amp; Server
+Verantwortlich:
+Siyar</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>1.4 QM &amp; Logistik
+Verantwortlich:
+Marco Schmidt</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>1.5 Rollout &amp; Übergabe
+Verantwortlich:
+Jan Kluth</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="n"/>
+      <c r="AB12" s="7" t="n"/>
+      <c r="AC12" s="7" t="n"/>
+      <c r="AD12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="7" t="n"/>
+      <c r="AB13" s="7" t="n"/>
+      <c r="AC13" s="7" t="n"/>
+      <c r="AD13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="7" t="n"/>
+      <c r="AB14" s="7" t="n"/>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="8" customHeight="1">
+      <c r="D15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="P15" s="8" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="AB15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>1.1.1 12x Standard-PCs
+Lenovo ThinkCentre M70s (SFF)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>1.2.1 16x Windows 11 Pro
+OEM-Lizenzen 64-Bit</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>1.3.1 Gigabit Verkabelung
+16x InLine Cat.6A Patchkabel</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>1.4.1 Wareneingangsprüfung
+Prüfung gem. § 377 HGB</t>
+        </is>
+      </c>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Z16" s="9" t="inlineStr">
+        <is>
+          <t>1.5.1 Staging im Systemhaus
+Vorinstallation im IT-Labor</t>
+        </is>
+      </c>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="8" customHeight="1">
+      <c r="D19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>1.1.2 4x CAD-Workstations
+Lenovo ThinkStation P3 (RTX Ada)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>1.2.2 16x M365 Business
+Office Standard Jahresabos</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>1.3.2 Fileserver-Kapazität
+445 GiB Speicherbedarf (Q1)</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>1.4.2 Mängelrüge Distributor
+Fristsetzung (Gehäuse &amp; Monitor)</t>
+        </is>
+      </c>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="10" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Z20" s="9" t="inlineStr">
+        <is>
+          <t>1.5.2 Montage vor Ort
+Ergonomie gem. ArbStättV</t>
+        </is>
+      </c>
+      <c r="AA20" s="10" t="n"/>
+      <c r="AB20" s="10" t="n"/>
+      <c r="AC20" s="10" t="n"/>
+      <c r="AD20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="10" t="n"/>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="10" t="n"/>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="10" t="n"/>
+      <c r="AC22" s="10" t="n"/>
+      <c r="AD22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="D23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>1.1.3 32x Ergonomie-Monitore
+Dell UltraSharp U2724D (27'' WQHD)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>1.2.3 16x Adobe Acrobat Pro
+PDF-Prüfung &amp; digitale Signatur</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="10" t="n"/>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>1.3.3 Energiekosten-Analyse
+1.771,26 € jährliche Stromkosten</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>1.4.3 Altdrucker-Entsorgung
+Fachgerecht nach ElektroG/WEEE</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="10" t="n"/>
+      <c r="Z24" s="9" t="inlineStr">
+        <is>
+          <t>1.5.3 Funktionstests
+Netzwerk, CAD &amp; Druckertest</t>
+        </is>
+      </c>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="10" t="n"/>
+      <c r="AC24" s="10" t="n"/>
+      <c r="AD24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="10" t="n"/>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="10" t="n"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="10" t="n"/>
+      <c r="AC25" s="10" t="n"/>
+      <c r="AD25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="10" t="n"/>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="n"/>
+      <c r="T26" s="10" t="n"/>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="10" t="n"/>
+      <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
+      <c r="AB26" s="10" t="n"/>
+      <c r="AC26" s="10" t="n"/>
+      <c r="AD26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="8" customHeight="1">
+      <c r="D27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>1.1.4 16x Eingabegeräte-Sets
+Logitech MK650 Business (Funk AES)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>1.2.4 16x ESET PROTECT
+Cloud EDR Endpoint Security</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="10" t="n"/>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>1.3.4 Switchport-Belegung
+Zuordnung Ports 1 bis 16</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="n"/>
+      <c r="T28" s="9" t="inlineStr">
+        <is>
+          <t>1.4.4 Datenschutz &amp; BSI
+Sichere 3-fache Festplattenlöschung</t>
+        </is>
+      </c>
+      <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n"/>
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="10" t="n"/>
+      <c r="Z28" s="9" t="inlineStr">
+        <is>
+          <t>1.5.4 Abnahmeprotokoll
+Rechtskonforme Unterzeichnung</t>
+        </is>
+      </c>
+      <c r="AA28" s="10" t="n"/>
+      <c r="AB28" s="10" t="n"/>
+      <c r="AC28" s="10" t="n"/>
+      <c r="AD28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="10" t="n"/>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="10" t="n"/>
+      <c r="AC29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="10" t="n"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="10" t="n"/>
+      <c r="AC30" s="10" t="n"/>
+      <c r="AD30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="8" customHeight="1">
+      <c r="D31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="P31" s="8" t="n"/>
+      <c r="V31" s="8" t="n"/>
+      <c r="AB31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>1.1.5 16x Externe SSDs
+Samsung Portable T7 Shield 1TB</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>1.2.5 Software-Images
+Vorinstallation &amp; Staging-Image</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>1.3.5 Server-Synchronisation
+Tägliche Sicherung der lokalen SSDs</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="T32" s="9" t="inlineStr">
+        <is>
+          <t>1.4.5 Entsorgungsnachweis
+Zertifikat für VektorPlan GmbH</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Z32" s="9" t="inlineStr">
+        <is>
+          <t>1.5.5 Projektcontrolling
+Soll-Ist: 46 Tage / im Budget</t>
+        </is>
+      </c>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="10" t="n"/>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="10" t="n"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="10" t="n"/>
+      <c r="AC33" s="10" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="10" t="n"/>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="n"/>
+      <c r="R34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="10" t="n"/>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="10" t="n"/>
+      <c r="AC34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="8" customHeight="1">
+      <c r="D35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="P35" s="8" t="n"/>
+      <c r="V35" s="8" t="n"/>
+      <c r="AB35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>1.1.6 1x Farblaser-MFP
+Lexmark CX930dse A3/A4 Drucker</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>1.2.6 Lizenzdokumentation
+Nachweis- &amp; Lizenzübersicht</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>1.3.6 Netzlaufwerke &amp; Rechte
+Konfiguration der Freigaben</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="T36" s="9" t="inlineStr">
+        <is>
+          <t>1.4.6 RMA-Abwicklung
+Nachlieferung der Tauschgeräte</t>
+        </is>
+      </c>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Z36" s="9" t="inlineStr">
+        <is>
+          <t>1.5.6 Lessons Learned
+Abschlusspräsentation vor Kunde</t>
+        </is>
+      </c>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="10" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="10" t="n"/>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="H24:L26"/>
+    <mergeCell ref="B20:F22"/>
+    <mergeCell ref="N24:R26"/>
+    <mergeCell ref="N20:R22"/>
+    <mergeCell ref="B16:F18"/>
+    <mergeCell ref="B32:F34"/>
+    <mergeCell ref="N36:R38"/>
+    <mergeCell ref="T24:X26"/>
+    <mergeCell ref="Z24:AD26"/>
+    <mergeCell ref="N32:R34"/>
+    <mergeCell ref="T32:X34"/>
+    <mergeCell ref="Z36:AD38"/>
+    <mergeCell ref="B3:AD3"/>
+    <mergeCell ref="H20:L22"/>
+    <mergeCell ref="B12:F14"/>
+    <mergeCell ref="N16:R18"/>
+    <mergeCell ref="T20:X22"/>
+    <mergeCell ref="Z16:AD18"/>
+    <mergeCell ref="Z32:AD34"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="T36:X38"/>
+    <mergeCell ref="N5:R7"/>
+    <mergeCell ref="N12:R14"/>
+    <mergeCell ref="T12:X14"/>
+    <mergeCell ref="Z12:AD14"/>
+    <mergeCell ref="B28:F30"/>
+    <mergeCell ref="H36:L38"/>
+    <mergeCell ref="H32:L34"/>
+    <mergeCell ref="H16:L18"/>
+    <mergeCell ref="Z20:AD22"/>
+    <mergeCell ref="B24:F26"/>
+    <mergeCell ref="N28:R30"/>
+    <mergeCell ref="T16:X18"/>
+    <mergeCell ref="H28:L30"/>
+    <mergeCell ref="B36:F38"/>
+    <mergeCell ref="T28:X30"/>
+    <mergeCell ref="Z28:AD30"/>
+    <mergeCell ref="H12:L14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -591,879 +1545,879 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Arbeitspaket-Uebersicht nach DIN 69901 (WBS - Work Breakdown Structure)</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Arbeitspaket-Übersicht nach DIN 69901 (WBS - Work Breakdown Structure)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>PSP-Code</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Teilprojekt / Arbeitspaket</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Detaillierte Beschreibung</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Verantwortlich</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Ergebnis / Deliverable</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>1.1 Hardware (Verantwortlich: Marian Bolecke)</t>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1.1 Hardware-Ausstattung (Verantwortlich: Marian Bolecke)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Standard-PCs</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>12x Lenovo ThinkCentre M70s</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>12x Standard-PCs</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Lenovo ThinkCentre M70s (SFF)</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>CAD-Workstations</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>4x Lenovo ThinkStation P3 Ada</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>4x CAD-Workstations</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Lenovo ThinkStation P3 (RTX Ada)</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Monitore</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>32x Dell UltraSharp 27'' WQHD</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>32x Ergonomie-Monitore</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Dell UltraSharp U2724D (27'' WQHD)</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Peripherie</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>16x Tastatur/Maus MK650 (AES)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>16x Eingabegeräte-Sets</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Logitech MK650 Business (Funk AES)</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Externe SSDs</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>16x Samsung T7 Shield 1TB</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>16x Externe SSDs</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Samsung Portable T7 Shield 1TB</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Farblaser-MFP</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>1x Lexmark CX930dse A3/A4</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>1x Farblaser-MFP</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Lexmark CX930dse A3/A4 Drucker</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>1.2 Software &amp; Lizenzen (Verantwortlich: Mathias Vonau)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Windows 11 Pro</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>16x OEM Pro 64-Bit</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>16x Windows 11 Pro</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>OEM-Lizenzen 64-Bit</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Microsoft 365</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>16x Business Standard Jahresabos</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>16x M365 Business</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Office Standard Jahresabos</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Adobe Acrobat Pro</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>16x PDF-Bearbeitung &amp; Signatur</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>16x Adobe Acrobat Pro</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>PDF-Prüfung &amp; digitale Signatur</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>ESET PROTECT</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>16x Cloud Endpoint Protection</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>16x ESET PROTECT</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Cloud EDR Endpoint Security</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Staging-Images</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Standardisiertes Sysprep-Image</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Software-Images</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Vorinstallation &amp; Staging-Image</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Treiber &amp; BIOS</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Firmware-Updates &amp; CAD-Treiber</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Lizenzdokumentation</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Nachweis- &amp; Lizenzübersicht</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>1.3 Netzwerk &amp; Infrastruktur (Verantwortlich: Siyar)</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>1.3 Netzwerk &amp; Server (Verantwortlich: Siyar)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Patchkabel</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>16x Cat.6a S/FTP (3m/5m)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Gigabit Verkabelung</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>16x InLine Cat.6A Patchkabel</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>1.3.2</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>LAN-Pruefung</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Messung der Ports &amp; Gigabit</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Fileserver-Kapazität</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>445 GiB Speicherbedarf (Q1)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>1.3.3</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>IP-Konfiguration</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Feste IPs &amp; DHCP-Reservierung</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Energiekosten-Analyse</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>1.771,26 € jährliche Stromkosten</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>1.3.4</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Netzlaufwerke</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Anbindung SMB/SharePoint</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Switchport-Belegung</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Zuordnung Ports 1 bis 16</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>1.3.5</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Druckereinbindung</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Printserver &amp; Scan-to-Mail</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Server-Synchronisation</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Tägliche Sicherung der lokalen SSDs</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>1.3.6</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Sicherheitscheck</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Firewall-Regeln &amp; VLAN</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Netzlaufwerke &amp; Rechte</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Konfiguration der Freigaben</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>1.4 Services &amp; Rollout (Verantwortlich: Marco Schmidt)</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>1.4 QM &amp; Logistik (Verantwortlich: Marco Schmidt)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>1.4.1</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Wareneingang</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Pruefung nach Paragraph 377 HGB</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Wareneingangsprüfung</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Prüfung gem. § 377 HGB</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>1.4.2</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Vorinstallation</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Hardware-Staging im Systemhaus</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Mängelrüge Distributor</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Fristsetzung (Gehäuse &amp; Monitor)</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>1.4.3</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Vor-Ort-Montage</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Ergonomische 2-Monitor-Arme</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Altdrucker-Entsorgung</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Fachgerecht nach ElektroG/WEEE</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>1.4.4</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Altdrucker-Recycling</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>ElektroG, WEEE &amp; BSI-Loeschung</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Datenschutz &amp; BSI</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Sichere 3-fache Festplattenlöschung</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>1.4.5</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Entsorgungsnachweis</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Zertifikat für VektorPlan GmbH</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Marco Schmidt</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>1.4.6</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>RMA-Abwicklung</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Nachlieferung der Tauschgeräte</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Marco Schmidt</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>1.5 Rollout &amp; Übergabe (Verantwortlich: Jan Kluth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Staging im Systemhaus</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Vorinstallation im IT-Labor</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Jan Kluth</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Montage vor Ort</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Ergonomie gem. ArbStättV</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Jan Kluth</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>1.5.3</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Funktionstests</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Stresstest CAD &amp; Peripherie</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Marco Schmidt</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>1.4.6</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Netzwerk, CAD &amp; Druckertest</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Jan Kluth</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>1.5.4</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>Abnahmeprotokoll</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Maengelfreie formelle Abnahme</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Marco Schmidt</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>1.5 Projektmanagement (Verantwortlich: Jan Kluth)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Projekt-Kick-off</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Auftragsklaerung &amp; Teamrollen</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Rechtskonforme Unterzeichnung</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>1.5.2</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Ablauf- &amp; Netzplan</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>DIN 69900 Termin-Controlling</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>1.5.5</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Projektcontrolling</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Soll-Ist: 46 Tage / im Budget</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>1.5.3</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Risikoanalyse</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Bewertungsmatrix &amp; Massnahmen</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Einsatzbereite Komponente / Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>1.5.6</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Lessons Learned</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Abschlusspräsentation vor Kunde</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>1.5.4</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Kalkulation &amp; NWA</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Preise &amp; Entscheidungsmatrix</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Jan Kluth</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>1.5.5</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Anwenderschulung</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Mitarbeitereinweisung Vor-Ort</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Jan Kluth</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Einsatzbereite Komponente / Dokument</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>1.5.6</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Lessons Learned</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Abschlussbericht &amp; Feedback</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Jan Kluth</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>

--- a/docs/01_Projektorganisation/Projektstrukturplan.xlsx
+++ b/docs/01_Projektorganisation/Projektstrukturplan.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001F497D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
@@ -66,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -95,7 +101,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F5F9"/>
+        <fgColor rgb="00F9FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF1F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +205,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,45 +588,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AD38"/>
+  <dimension ref="B2:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.5" customWidth="1" min="1" max="1"/>
-    <col width="7.5" customWidth="1" min="2" max="2"/>
-    <col width="7.5" customWidth="1" min="3" max="3"/>
-    <col width="7.5" customWidth="1" min="4" max="4"/>
-    <col width="7.5" customWidth="1" min="5" max="5"/>
-    <col width="7.5" customWidth="1" min="6" max="6"/>
-    <col width="7.5" customWidth="1" min="7" max="7"/>
-    <col width="7.5" customWidth="1" min="8" max="8"/>
-    <col width="7.5" customWidth="1" min="9" max="9"/>
-    <col width="7.5" customWidth="1" min="10" max="10"/>
-    <col width="7.5" customWidth="1" min="11" max="11"/>
-    <col width="7.5" customWidth="1" min="12" max="12"/>
-    <col width="7.5" customWidth="1" min="13" max="13"/>
-    <col width="7.5" customWidth="1" min="14" max="14"/>
-    <col width="7.5" customWidth="1" min="15" max="15"/>
-    <col width="7.5" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="7.5" customWidth="1" min="18" max="18"/>
-    <col width="7.5" customWidth="1" min="19" max="19"/>
-    <col width="7.5" customWidth="1" min="20" max="20"/>
-    <col width="7.5" customWidth="1" min="21" max="21"/>
-    <col width="7.5" customWidth="1" min="22" max="22"/>
-    <col width="7.5" customWidth="1" min="23" max="23"/>
-    <col width="7.5" customWidth="1" min="24" max="24"/>
-    <col width="7.5" customWidth="1" min="25" max="25"/>
-    <col width="7.5" customWidth="1" min="26" max="26"/>
-    <col width="7.5" customWidth="1" min="27" max="27"/>
-    <col width="7.5" customWidth="1" min="28" max="28"/>
-    <col width="7.5" customWidth="1" min="29" max="29"/>
-    <col width="7.5" customWidth="1" min="30" max="30"/>
-    <col width="7.5" customWidth="1" min="31" max="31"/>
-    <col width="7.5" customWidth="1" min="32" max="32"/>
-    <col width="7.5" customWidth="1" min="33" max="33"/>
-    <col width="7.5" customWidth="1" min="34" max="34"/>
+    <col width="3.2" customWidth="1" min="1" max="1"/>
+    <col width="6.4" customWidth="1" min="2" max="2"/>
+    <col width="6.4" customWidth="1" min="3" max="3"/>
+    <col width="6.4" customWidth="1" min="4" max="4"/>
+    <col width="6.4" customWidth="1" min="5" max="5"/>
+    <col width="6.4" customWidth="1" min="6" max="6"/>
+    <col width="3.2" customWidth="1" min="7" max="7"/>
+    <col width="6.4" customWidth="1" min="8" max="8"/>
+    <col width="6.4" customWidth="1" min="9" max="9"/>
+    <col width="6.4" customWidth="1" min="10" max="10"/>
+    <col width="6.4" customWidth="1" min="11" max="11"/>
+    <col width="6.4" customWidth="1" min="12" max="12"/>
+    <col width="3.2" customWidth="1" min="13" max="13"/>
+    <col width="6.4" customWidth="1" min="14" max="14"/>
+    <col width="6.4" customWidth="1" min="15" max="15"/>
+    <col width="6.4" customWidth="1" min="16" max="16"/>
+    <col width="6.4" customWidth="1" min="17" max="17"/>
+    <col width="6.4" customWidth="1" min="18" max="18"/>
+    <col width="3.2" customWidth="1" min="19" max="19"/>
+    <col width="6.4" customWidth="1" min="20" max="20"/>
+    <col width="6.4" customWidth="1" min="21" max="21"/>
+    <col width="6.4" customWidth="1" min="22" max="22"/>
+    <col width="6.4" customWidth="1" min="23" max="23"/>
+    <col width="6.4" customWidth="1" min="24" max="24"/>
+    <col width="3.2" customWidth="1" min="25" max="25"/>
+    <col width="6.4" customWidth="1" min="26" max="26"/>
+    <col width="6.4" customWidth="1" min="27" max="27"/>
+    <col width="6.4" customWidth="1" min="28" max="28"/>
+    <col width="6.4" customWidth="1" min="29" max="29"/>
+    <col width="6.4" customWidth="1" min="30" max="30"/>
+    <col width="3.2" customWidth="1" min="31" max="31"/>
+    <col width="6.4" customWidth="1" min="32" max="32"/>
+    <col width="6.4" customWidth="1" min="33" max="33"/>
+    <col width="6.4" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
+    <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -623,16 +638,17 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Projekt: IT-Ausstattung Planungs- und Konstruktionsbüro | Kunde: VektorPlan GmbH | Projektleiter: Jan Kluth</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
+          <t>Projekt: IT-Ausstattung Planungs- und Konstruktionsbüro | Kunde: VektorPlan GmbH | Projektleiter: Jan Kluth | 5 Teilprojekte, 30 Arbeitspakete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="19" customHeight="1">
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>1.0 IT-Ausstattung VektorPlan GmbH
-(Schlüsselfertige Büro-Ausstattung)
-Projektleiter: Jan Kluth</t>
+(Schlüsselfertige Büro-Gesamtausstattung)
+Projektleitung: Jan Kluth</t>
         </is>
       </c>
       <c r="O5" s="4" t="n"/>
@@ -640,24 +656,24 @@
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="19" customHeight="1">
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="19" customHeight="1">
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
     </row>
-    <row r="8" ht="12" customHeight="1">
+    <row r="8" ht="10" customHeight="1">
       <c r="P8" s="5" t="n"/>
     </row>
-    <row r="9" ht="12" customHeight="1">
+    <row r="9" ht="10" customHeight="1">
       <c r="P9" s="5" t="n"/>
     </row>
     <row r="10" ht="6" customHeight="1">
@@ -1483,12 +1499,21 @@
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
     </row>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>PROJEKTSTRUKTURPLAN (PSP) NACH DIN 69901  |  5 TEILPROJEKTE  |  30 ARBEITSPAKETE  |  VOLLSTÄNDIGE LIEFERUNG &amp; INBETRIEBNAHME</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="H24:L26"/>
     <mergeCell ref="B20:F22"/>
     <mergeCell ref="N24:R26"/>
     <mergeCell ref="N20:R22"/>
+    <mergeCell ref="B41:AD41"/>
     <mergeCell ref="B16:F18"/>
     <mergeCell ref="B32:F34"/>
     <mergeCell ref="N36:R38"/>
@@ -1545,879 +1570,879 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Arbeitspaket-Übersicht nach DIN 69901 (WBS - Work Breakdown Structure)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>PSP-Code</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Teilprojekt / Arbeitspaket</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Detaillierte Beschreibung</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Verantwortlich</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Ergebnis / Deliverable</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>1.1 Hardware-Ausstattung (Verantwortlich: Marian Bolecke)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>12x Standard-PCs</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Lenovo ThinkCentre M70s (SFF)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>4x CAD-Workstations</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Lenovo ThinkStation P3 (RTX Ada)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>32x Ergonomie-Monitore</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Dell UltraSharp U2724D (27'' WQHD)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>1.1.4</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>16x Eingabegeräte-Sets</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Logitech MK650 Business (Funk AES)</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>1.1.5</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>16x Externe SSDs</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Samsung Portable T7 Shield 1TB</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>1.1.6</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>1x Farblaser-MFP</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Lexmark CX930dse A3/A4 Drucker</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Marian Bolecke</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>1.2 Software &amp; Lizenzen (Verantwortlich: Mathias Vonau)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>16x Windows 11 Pro</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>OEM-Lizenzen 64-Bit</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>16x M365 Business</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Office Standard Jahresabos</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>16x Adobe Acrobat Pro</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>PDF-Prüfung &amp; digitale Signatur</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>16x ESET PROTECT</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Cloud EDR Endpoint Security</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>1.2.5</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Software-Images</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Vorinstallation &amp; Staging-Image</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>1.2.6</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Lizenzdokumentation</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Nachweis- &amp; Lizenzübersicht</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Mathias Vonau</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>1.3 Netzwerk &amp; Server (Verantwortlich: Siyar)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Gigabit Verkabelung</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>16x InLine Cat.6A Patchkabel</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>1.3.2</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Fileserver-Kapazität</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>445 GiB Speicherbedarf (Q1)</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>1.3.3</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Energiekosten-Analyse</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>1.771,26 € jährliche Stromkosten</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>1.3.4</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Switchport-Belegung</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Zuordnung Ports 1 bis 16</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>1.3.5</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Server-Synchronisation</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Tägliche Sicherung der lokalen SSDs</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>1.3.6</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Netzlaufwerke &amp; Rechte</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Konfiguration der Freigaben</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>Siyar</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>1.4 QM &amp; Logistik (Verantwortlich: Marco Schmidt)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>1.4.1</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Wareneingangsprüfung</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Prüfung gem. § 377 HGB</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>1.4.2</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Mängelrüge Distributor</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Fristsetzung (Gehäuse &amp; Monitor)</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>1.4.3</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Altdrucker-Entsorgung</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Fachgerecht nach ElektroG/WEEE</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>1.4.4</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Datenschutz &amp; BSI</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Sichere 3-fache Festplattenlöschung</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>1.4.5</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Entsorgungsnachweis</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Zertifikat für VektorPlan GmbH</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>1.4.6</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>RMA-Abwicklung</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Nachlieferung der Tauschgeräte</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>Marco Schmidt</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>1.5 Rollout &amp; Übergabe (Verantwortlich: Jan Kluth)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>1.5.1</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Staging im Systemhaus</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Vorinstallation im IT-Labor</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>1.5.2</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Montage vor Ort</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Ergonomie gem. ArbStättV</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>1.5.3</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Funktionstests</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Netzwerk, CAD &amp; Druckertest</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>1.5.4</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Abnahmeprotokoll</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Rechtskonforme Unterzeichnung</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>1.5.5</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Projektcontrolling</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Soll-Ist: 46 Tage / im Budget</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>1.5.6</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Lessons Learned</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Abschlusspräsentation vor Kunde</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Jan Kluth</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Einsatzbereite Komponente / Dokument</t>
         </is>

--- a/docs/01_Projektorganisation/Projektstrukturplan.xlsx
+++ b/docs/01_Projektorganisation/Projektstrukturplan.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,20 +29,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00595959"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -52,24 +46,42 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F497D"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F497D"/>
+      <color rgb="00333333"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="00000000"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="9">
@@ -81,7 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,27 +108,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="00BFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4C6E7"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9FAFC"/>
+        <fgColor rgb="00E6E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF1F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005B9BD5"/>
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,44 +137,44 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F497D"/>
+        <color rgb="00333333"/>
       </left>
       <right style="medium">
-        <color rgb="001F497D"/>
+        <color rgb="00333333"/>
       </right>
       <top style="medium">
-        <color rgb="001F497D"/>
+        <color rgb="00333333"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F497D"/>
+        <color rgb="00333333"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="002F5597"/>
+        <color rgb="00595959"/>
       </left>
       <right style="medium">
-        <color rgb="002F5597"/>
+        <color rgb="00595959"/>
       </right>
       <top style="medium">
-        <color rgb="002F5597"/>
+        <color rgb="00595959"/>
       </top>
       <bottom style="medium">
-        <color rgb="002F5597"/>
+        <color rgb="00595959"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="008EA9DB"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="008EA9DB"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="008EA9DB"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="008EA9DB"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
     <border>
@@ -191,11 +203,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -205,22 +217,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,14 +640,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Projektstrukturplan (PSP) nach DIN 69901</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Projekt: IT-Ausstattung Planungs- und Konstruktionsbüro | Kunde: VektorPlan GmbH | Projektleiter: Jan Kluth | 5 Teilprojekte, 30 Arbeitspakete</t>
@@ -676,7 +688,7 @@
     <row r="9" ht="10" customHeight="1">
       <c r="P9" s="5" t="n"/>
     </row>
-    <row r="10" ht="6" customHeight="1">
+    <row r="10" ht="5" customHeight="1">
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -1500,10 +1512,10 @@
       <c r="AD38" s="10" t="n"/>
     </row>
     <row r="40" ht="10" customHeight="1"/>
-    <row r="41" ht="24" customHeight="1">
+    <row r="41" ht="22" customHeight="1">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>PROJEKTSTRUKTURPLAN (PSP) NACH DIN 69901  |  5 TEILPROJEKTE  |  30 ARBEITSPAKETE  |  VOLLSTÄNDIGE LIEFERUNG &amp; INBETRIEBNAHME</t>
+          <t>PROJEKTSTRUKTURPLAN (PSP) NACH DIN 69901  |  5 TEILPROJEKTE  |  30 ARBEITSPAKETE</t>
         </is>
       </c>
     </row>
@@ -1569,14 +1581,14 @@
     <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Arbeitspaket-Übersicht nach DIN 69901 (WBS - Work Breakdown Structure)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
           <t>PSP-Code</t>
@@ -1603,7 +1615,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>1.1 Hardware-Ausstattung (Verantwortlich: Marian Bolecke)</t>
@@ -1772,7 +1784,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>1.2 Software &amp; Lizenzen (Verantwortlich: Mathias Vonau)</t>
@@ -1941,7 +1953,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>1.3 Netzwerk &amp; Server (Verantwortlich: Siyar)</t>
@@ -2110,7 +2122,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
+    <row r="25" ht="20" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>1.4 QM &amp; Logistik (Verantwortlich: Marco Schmidt)</t>
@@ -2279,7 +2291,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
           <t>1.5 Rollout &amp; Übergabe (Verantwortlich: Jan Kluth)</t>
